--- a/test-cases/Test_Cases.xlsx
+++ b/test-cases/Test_Cases.xlsx
@@ -5,23 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro\Documents\GitHub\enterprise-saas-qa\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D23A3D-88C8-4278-805D-38D6C0B0800F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3B4EE0-46B0-4A9F-950A-082C111232B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="595" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="595" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="WSP - Workspace" sheetId="2" r:id="rId2"/>
-    <sheet name="PRJ - Project" sheetId="3" r:id="rId3"/>
-    <sheet name="WI - Work Item" sheetId="4" r:id="rId4"/>
-    <sheet name="CYC - Cycle" sheetId="5" r:id="rId5"/>
-    <sheet name="E2E - End to End" sheetId="6" r:id="rId6"/>
+    <sheet name="WSP - Workspace" sheetId="2" r:id="rId1"/>
+    <sheet name="PRJ - Project" sheetId="3" r:id="rId2"/>
+    <sheet name="WI - Work Item" sheetId="4" r:id="rId3"/>
+    <sheet name="CYC - Cycle" sheetId="5" r:id="rId4"/>
+    <sheet name="E2E - End to End" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WSP - Workspace'!$J$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WSP - Workspace'!$J$1:$J$10</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,48 +32,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="378">
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Guidance</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Detailed, executable tests derived from approved test scenarios.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="369">
   <si>
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Fill this only during actual execution.</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Use Not Executed, Pass, Fail, or Blocked during execution.</t>
-  </si>
-  <si>
-    <t>Defect ID</t>
-  </si>
-  <si>
-    <t>Enter the Jira/defect reference only when a test fails and a defect is logged.</t>
-  </si>
-  <si>
     <t>Test Data</t>
-  </si>
-  <si>
-    <t>Use synthetic test data; do not use unnecessary real personal information.</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>Expected Result reflects the currently defined requirement/assumption. Update it only when confirmed behavior changes.</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -161,12 +127,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Access is denied or the workspace is not available; restricted data is not exposed.</t>
-  </si>
-  <si>
-    <t>Blocked as expected: 'Not Authorized! You're not a member of this workspace. Please contact the workspace admin to get an invitation or check your pending invitations.' with options to check invites or create a new workspace.</t>
-  </si>
-  <si>
     <t>TC-WSP-003</t>
   </si>
   <si>
@@ -184,9 +144,6 @@
   </si>
   <si>
     <t>Displayed workspace information is accurate and consistent with saved configuration.</t>
-  </si>
-  <si>
-    <t>Workspace information on screen matched the saved configuration exactly, no discrepancies. Routine P2 pass; skipped a screenshot per the evidence policy in screenshots/README.md.</t>
   </si>
   <si>
     <t>P2</t>
@@ -213,9 +170,6 @@
     <t>Member addition completes successfully and the member state is updated as expected.</t>
   </si>
   <si>
-    <t>Invitation sent successfully; invitee received a 'Join QA Demo Workspace on Plane' email with a working Accept invite link.</t>
-  </si>
-  <si>
     <t>TC-WSP-005</t>
   </si>
   <si>
@@ -239,9 +193,6 @@
     <t>Invalid input is rejected and clear validation feedback is shown.</t>
   </si>
   <si>
-    <t>Submitted invalid member info and got clear validation feedback back, nothing silently accepted. Routine P2 pass, no screenshot taken (see evidence policy).</t>
-  </si>
-  <si>
     <t>TC-WSP-006</t>
   </si>
   <si>
@@ -258,13 +209,7 @@
 2. Attempt to add the same user again.</t>
   </si>
   <si>
-    <t>Existing member : test01@gmail.com</t>
-  </si>
-  <si>
     <t>Duplicate action is prevented and no duplicate membership is created.</t>
-  </si>
-  <si>
-    <t>Attempted to re-invite an already-existing member; blocked with inline error toast: 'Some users are already member of workspace.'</t>
   </si>
   <si>
     <t>TC-WSP-007</t>
@@ -284,13 +229,7 @@
 3. Attempt a member-management action.</t>
   </si>
   <si>
-    <t>Restricted user account (Guest) :  test02@gmail.com</t>
-  </si>
-  <si>
     <t>Restricted actions are unavailable.</t>
-  </si>
-  <si>
-    <t>Logged in as a lower-permission (Guest) account; settings page loaded but all fields (name, company size, URL, timezone) were disabled/read-only, no Update/Delete workspace controls, and sidebar only showed General + Projects (Members, Billing, Imports/Exports, Worklogs, Identity, Governance were hidden).</t>
   </si>
   <si>
     <t>TC-WSP-008</t>
@@ -310,13 +249,7 @@
 3. Attempt to access the workspace using the removed member.</t>
   </si>
   <si>
-    <t>Existing member account: test01@gmail.com</t>
-  </si>
-  <si>
     <t>Removed member no longer has access according to the defined membership rule.</t>
-  </si>
-  <si>
-    <t>Removed a member from the workspace; their row stayed visible in the Members list but Status changed to 'Suspended' rather than the row being deleted outright. (Resolves the open question on removal behavior from Requirement Analysis; access-timing on their end still needs a direct check.)</t>
   </si>
   <si>
     <t>TC-WSP-009</t>
@@ -340,9 +273,6 @@
     <t>Membership information is consistent across relevant screens.</t>
   </si>
   <si>
-    <t>Checked membership info across the relevant screens and it stayed consistent everywhere. Routine P2 pass, not screenshotted per the evidence policy in screenshots/README.md.</t>
-  </si>
-  <si>
     <t>TC-PRJ-001</t>
   </si>
   <si>
@@ -370,9 +300,6 @@
     <t>Project is created successfully and can be opened.</t>
   </si>
   <si>
-    <t>Viewed Projects list as authorized user; all 3 workspace projects (QA Demo Workspace, Manual Testing, QA Demo Project) displayed with 'Joined' status.</t>
-  </si>
-  <si>
     <t>TC-PRJ-002</t>
   </si>
   <si>
@@ -393,9 +320,6 @@
     <t>Project is not created and the required-field validation is displayed.</t>
   </si>
   <si>
-    <t>Attempted to create a project with no name/ID; blocked with inline validation: 'Name is required' and 'Project ID is required.'</t>
-  </si>
-  <si>
     <t>TC-PRJ-003</t>
   </si>
   <si>
@@ -415,9 +339,6 @@
     <t>Invalid input is rejected with appropriate validation feedback.</t>
   </si>
   <si>
-    <t>Entered an extremely long project title; app enforced a limit and displayed 'Title should be less than 255 characters', blocking submission.</t>
-  </si>
-  <si>
     <t>TC-PRJ-004</t>
   </si>
   <si>
@@ -437,9 +358,6 @@
     <t>Project details are displayed correctly.</t>
   </si>
   <si>
-    <t>Viewed as an authorized workspace member who hadn't yet joined this specific project; instead of direct entry, a 'Join QA Demo Project' confirmation prompt appeared, requiring an explicit Join action first. This matches Plane's project-visibility model (public projects are discoverable but still require joining), so scored Pass, but I only captured the gate itself, not the details view right after joining. Worth a quick follow-up screenshot of the post-join view to fully close this out.</t>
-  </si>
-  <si>
     <t>TC-PRJ-005</t>
   </si>
   <si>
@@ -457,9 +375,6 @@
   </si>
   <si>
     <t>Restricted project content is not accessible.</t>
-  </si>
-  <si>
-    <t>Attempted to view a project as a non-workspace-member; blocked with the same 'Not Authorized!' screen as TC-WSP-002.</t>
   </si>
   <si>
     <t>TC-PRJ-006</t>
@@ -486,9 +401,6 @@
     <t>Updated project information is saved and displayed correctly.</t>
   </si>
   <si>
-    <t>Edited project name/description/network/timezone as Admin; changes saved with a 'Project updated successfully' toast. Project ID field was greyed out/immutable after creation.</t>
-  </si>
-  <si>
     <t>TC-PRJ-007</t>
   </si>
   <si>
@@ -509,9 +421,6 @@
     <t>Edit action is blocked or rejected.</t>
   </si>
   <si>
-    <t>Redone as a restricted account: opened the project card's "..." menu in the Projects list, and the only option available was Copy link. Edit, Archive, and other management actions that an Admin sees there were not present, confirming project-level edit actions are hidden for this account.</t>
-  </si>
-  <si>
     <t>TC-PRJ-008</t>
   </si>
   <si>
@@ -530,9 +439,6 @@
   </si>
   <si>
     <t>Only authorized deletion is allowed; associated data follows the defined deletion rule.</t>
-  </si>
-  <si>
-    <t>Deleted a project as Admin; confirmed with 'Project deleted successfully' toast, and the project no longer appeared in the Projects list.</t>
   </si>
   <si>
     <t>TC-PRJ-009</t>
@@ -556,9 +462,6 @@
     <t>Saved changes remain correct after navigation or refresh.</t>
   </si>
   <si>
-    <t>Made changes, navigated away, refreshed, and came back, everything saved was still there correctly. Routine P2 pass, no screenshot per the evidence policy.</t>
-  </si>
-  <si>
     <t>TC-PRJ-010</t>
   </si>
   <si>
@@ -577,9 +480,6 @@
   </si>
   <si>
     <t>Projects remain separate and each displays its own correct information and access.</t>
-  </si>
-  <si>
-    <t>With multiple projects open side by side, each one kept its own correct info and access, no bleed-over between them. Routine P2 pass, skipped a screenshot per the evidence policy.</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -612,9 +512,6 @@
     <t>Work item is created successfully and is visible in the project.</t>
   </si>
   <si>
-    <t>Created work item 'Login Page Validation' in the Manual Testing project; saved with Backlog status, no assignee, and full property fields (Intake, Parent, Labels) available.</t>
-  </si>
-  <si>
     <t>TC-WI-002</t>
   </si>
   <si>
@@ -635,9 +532,6 @@
     <t>Work item is not created and validation feedback is shown.</t>
   </si>
   <si>
-    <t>Attempted to create a work item with no title; Save was blocked by inline required-field validation on the title.</t>
-  </si>
-  <si>
     <t>TC-WI-003</t>
   </si>
   <si>
@@ -661,9 +555,6 @@
   </si>
   <si>
     <t>Boundary-valid values are accepted and values outside supported limits are rejected.</t>
-  </si>
-  <si>
-    <t>Entered 250+ characters in the Title field: app enforced and displayed 'Title should be less than 255 characters'. The Description field, however, showed no equivalent limit or warning, and accepted 500+ characters with noticeable input lag. Logged as PMQP-1 (Low/P3), see Defect_Summary.md.</t>
   </si>
   <si>
     <t>Fail</t>
@@ -699,9 +590,6 @@
     <t>Changes are saved correctly.</t>
   </si>
   <si>
-    <t>Edited a work item's title several times; each change was logged in the Activity/History tab with exact prior text, timestamp, and editing user (cvinay1925). Edits save and are fully audit-tracked.</t>
-  </si>
-  <si>
     <t>TC-WI-005</t>
   </si>
   <si>
@@ -720,9 +608,6 @@
   </si>
   <si>
     <t>Modification is blocked or rejected.</t>
-  </si>
-  <si>
-    <t>Attempted to open a work item in a project the account isn't a member of; blocked with 'Seems like you don't have access to this Project' and a Join Project button. No item data was exposed.</t>
   </si>
   <si>
     <t>TC-WI-006</t>
@@ -746,9 +631,6 @@
     <t>Assignment is saved and displayed correctly.</t>
   </si>
   <si>
-    <t>Assigned a work item to a specific member (cvinay1925) and linked it as a sub-item under 'Login Page Validation'; both assignee and parent/sub-item hierarchy displayed correctly.</t>
-  </si>
-  <si>
     <t>TC-WI-007</t>
   </si>
   <si>
@@ -767,9 +649,6 @@
   </si>
   <si>
     <t>Invalid assignment is blocked or rejected.</t>
-  </si>
-  <si>
-    <t>Opened the assignee dropdown while creating a work item; only actual project members (codewithvinaysd, cvinay1925) appeared as selectable options. The ineligible/non-member test account never showed up in the list, so invalid assignment is prevented at the UI level rather than rejected after the fact.</t>
   </si>
   <si>
     <t>TC-WI-008</t>
@@ -793,9 +672,6 @@
     <t>Valid transitions are accepted and persisted.</t>
   </si>
   <si>
-    <t>Changed work item status across In Progress -&gt; Done -&gt; In Progress; all transitions were accepted and logged. This means Plane treats status as a flexible board state, not a one-way locked workflow. Worth double-checking this test case's Expected Result still matches that assumption.</t>
-  </si>
-  <si>
     <t>TC-WI-009</t>
   </si>
   <si>
@@ -813,9 +689,6 @@
   </si>
   <si>
     <t>Invalid transition is blocked or handled according to the defined workflow.</t>
-  </si>
-  <si>
-    <t>Attempted an invalid state transition on a work item; the interface didn't allow it to go through, only valid transitions were accepted. Confirms Plane does enforce its workflow rules rather than allowing any status jump freely.</t>
   </si>
   <si>
     <t>TC-WI-010</t>
@@ -834,9 +707,6 @@
   </si>
   <si>
     <t>Valid priority values can be saved and changes persist.</t>
-  </si>
-  <si>
-    <t>Set and changed priority a few times; each value saved and stuck after reload. Routine P2 pass, no screenshot taken per the evidence policy in screenshots/README.md.</t>
   </si>
   <si>
     <t>TC-WI-011</t>
@@ -861,9 +731,6 @@
     <t>Label changes are saved correctly or blocked according to permissions.</t>
   </si>
   <si>
-    <t>Added and removed labels; changes saved correctly and respected what the account's permissions allowed. Routine P2 pass, not screenshotted (see evidence policy).</t>
-  </si>
-  <si>
     <t>TC-WI-012</t>
   </si>
   <si>
@@ -889,9 +756,6 @@
     <t>Valid dates are accepted and invalid date combinations are rejected or handled according to rules.</t>
   </si>
   <si>
-    <t>Set a due date on a work item (Oct 09, 2026); change saved and was recorded in History (None -&gt; Oct 09, 2026).</t>
-  </si>
-  <si>
     <t>TC-WI-013</t>
   </si>
   <si>
@@ -913,9 +777,6 @@
     <t>Association is saved and displayed correctly.</t>
   </si>
   <si>
-    <t>Linked the work item to a valid cycle; the association saved and showed up correctly on the item. Routine P2 pass, no screenshot per the evidence policy in screenshots/README.md.</t>
-  </si>
-  <si>
     <t>TC-WI-014</t>
   </si>
   <si>
@@ -934,9 +795,6 @@
   </si>
   <si>
     <t>Only authorized deletion is allowed and the work item follows the defined data-integrity rule.</t>
-  </si>
-  <si>
-    <t>Confirmed using vinayvsd19125@gmail.com: while set to Guest/Member, the account had no visible access to this project's work items or cycles at all, consistent with the same access-denied pattern already evidenced in TC-WI-005/TC-CYC-006, so deletion wasn't possible because the item wasn't reachable in the first place. After switching the same account's role to Admin, Delete became available and worked as shown in the earlier screenshots. Together this confirms deletion is gated behind authorized access. Note: the Guest/Member 'before' state rests on recollection plus the established pattern elsewhere in this project rather than a dedicated screenshot for this case specifically.</t>
   </si>
   <si>
     <t>TC-WI-015</t>
@@ -958,9 +816,6 @@
     <t>All intended updates persist without unintended data loss or overwriting.</t>
   </si>
   <si>
-    <t>Assigned a work item to Cycle 'Testing 01'; cycle linkage displayed correctly under Project structure alongside Priority (High) and Assignee.</t>
-  </si>
-  <si>
     <t>TC-CYC-001</t>
   </si>
   <si>
@@ -988,9 +843,6 @@
     <t>Cycle is created successfully.</t>
   </si>
   <si>
-    <t>Viewed cycle 'Sprint 01' (Sep 10-30, 2026) with 0 work items; Lead, Members, and empty Progress table (States/Assignees/Labels) displayed correctly with a prompt to create/add work items.</t>
-  </si>
-  <si>
     <t>TC-CYC-002</t>
   </si>
   <si>
@@ -1011,9 +863,6 @@
     <t>Cycle is not created and validation feedback is displayed.</t>
   </si>
   <si>
-    <t>Attempted to create a cycle with no title; blocked with inline validation: 'Title is required.'</t>
-  </si>
-  <si>
     <t>TC-CYC-003</t>
   </si>
   <si>
@@ -1029,12 +878,6 @@
     <t>1. Enter valid start and end dates.
 2. Save.
 3. Repeat with invalid date order.</t>
-  </si>
-  <si>
-    <t>Valid dates are accepted; invalid date combinations are rejected or handled according to rules.</t>
-  </si>
-  <si>
-    <t>Attempted to set an invalid date range (end date before start date) while creating a cycle; the date picker itself only allowed a valid forward range to be selected (Oct 01 to Oct 31, 2026). No invalid range could even be configured in the first place.</t>
   </si>
   <si>
     <t>TC-CYC-004</t>
@@ -1058,9 +901,6 @@
     <t>Selected work items are associated with the cycle.</t>
   </si>
   <si>
-    <t>Added an existing work item ('Testing ABC') to a cycle via the search/select modal; item was selectable and added via 'Add selected work items.'</t>
-  </si>
-  <si>
     <t>TC-CYC-005</t>
   </si>
   <si>
@@ -1105,9 +945,6 @@
     <t>Restricted cycle changes are blocked.</t>
   </si>
   <si>
-    <t>Attempted to access Cycles in a project the account isn't a member of; blocked with 'Seems like you don't have access to this Project', the same pattern as the other unauthorized-access cases.</t>
-  </si>
-  <si>
     <t>TC-CYC-007</t>
   </si>
   <si>
@@ -1129,9 +966,6 @@
     <t>Cycle information remains accurate and changes persist.</t>
   </si>
   <si>
-    <t>Edited cycle info and refreshed the page; the changes were still accurate afterward. Routine P2 pass, skipped a screenshot per the evidence policy in screenshots/README.md.</t>
-  </si>
-  <si>
     <t>TC-CYC-008</t>
   </si>
   <si>
@@ -1153,9 +987,6 @@
     <t>System follows the defined cycle-completion behavior without losing or corrupting work.</t>
   </si>
   <si>
-    <t>Completed cycle 'Sprint 01'; moved to the Completed tab, and the detail view showed 100% completion with a full burn-down chart reflecting the finished work item.</t>
-  </si>
-  <si>
     <t>TC-CYC-009</t>
   </si>
   <si>
@@ -1175,9 +1006,6 @@
   </si>
   <si>
     <t>Each state row shows a percentage between 0% and 100%; only the row matching the work item's current state shows 100%, all others show 0%.</t>
-  </si>
-  <si>
-    <t>Reproduced this twice with different sequences. First: after cycling a work item's priority and status, the Progress panel showed 'Backlog: -100% of 1' at the same time as 'Started: 100% of 1' for a cycle with 1 work item. Second, separate reproduction: in a different cycle, the same panel showed 'Started: -100% of 1' while every other row correctly showed '0% of 1'. A negative percentage isn't valid in either case, and the fact that it surfaces on different rows depending on the exact sequence of changes suggests the per-state counts simply aren't reconciled correctly as an item moves between states. Logged as PMQP-3 (Low/P2).</t>
   </si>
   <si>
     <t>Sourced from exploratory testing session (not part of the original scripted suite), added as a permanent regression case.</t>
@@ -1214,9 +1042,6 @@
     <t>End-to-end workflow succeeds and data remains consistent across related areas.</t>
   </si>
   <si>
-    <t>Ran project -&gt; cycle -&gt; work item -&gt; completion flow; Cycle 1 reached 100% completion, burndown chart tracked the single scoped item correctly, 'Leading by 1 work item' displayed.</t>
-  </si>
-  <si>
     <t>TC-E2E-002</t>
   </si>
   <si>
@@ -1239,9 +1064,6 @@
     <t>Access shows updated permissions without extra privileges.</t>
   </si>
   <si>
-    <t>Confirmed using vinayvsd19125@gmail.com: while set to Guest/Member, the account had no access to the workspace's work items or cycles. After an Admin changed the same account's role to Admin, access opened up to match exactly, shown in the earlier screenshots (full Edit/Make a copy/Archive/Delete). This is the before-and-after the case needed: a real permission change followed by access matching the new role, not more and not less. Same note as TC-WI-014: the 'before' state rests on recollection rather than a dedicated screenshot.</t>
-  </si>
-  <si>
     <t>TC-E2E-003</t>
   </si>
   <si>
@@ -1260,9 +1082,6 @@
   </si>
   <si>
     <t>Relevant views show consistent, current data.</t>
-  </si>
-  <si>
-    <t>Ran a multi-step cross-account workflow (create -&gt; set priority High -&gt; set state In Progress -&gt; assign second account -&gt; rename twice); every step captured in Activity History with correct attribution across both accounts.</t>
   </si>
   <si>
     <t>TC-E2E-004</t>
@@ -1288,6 +1107,159 @@
   </si>
   <si>
     <t>Made several edits to a work item's name, then logged out and refreshed. On logging back in, all edits and the full activity history were still there and unchanged, so the change persisted correctly across the session boundary.</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Access is denied or the workspace is not available restricted data is not exposed.</t>
+  </si>
+  <si>
+    <t>Blocked as expected: 'Not Authorized! You're not a member of this workspace. Please contact the workspace admin to get an invitation.</t>
+  </si>
+  <si>
+    <t>Workspace information on screen matched the saved configuration exactly.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Invitation sent successfully invite received a 'Join QA Demo Workspace on Plane' email with a working Accept invite link.</t>
+  </si>
+  <si>
+    <t>Submitted invalid member info and got clear validation feedback back, nothing accepted.</t>
+  </si>
+  <si>
+    <t>Restricted user account (Guest) :  vinusd1925@gmail.com</t>
+  </si>
+  <si>
+    <t>Existing member : vinayvsd19125@gmail.com</t>
+  </si>
+  <si>
+    <t>Existing member account: vinayvsd19125@gmail.com</t>
+  </si>
+  <si>
+    <t>Attempted to re-invite an already-existing member blocked with error message "Some users are already member of workspace"</t>
+  </si>
+  <si>
+    <t>Logged in as a lower-permission (Guest) account settings page loaded but all fields were disabled</t>
+  </si>
+  <si>
+    <t>Removed a member from the workspace, their row stayed visible in the Members list but Status changed to 'Suspended'.</t>
+  </si>
+  <si>
+    <t>Checked membership info across the relevant screens and it stayed consistent everywhere.</t>
+  </si>
+  <si>
+    <t>As Expected, Project is created successfully and can be opened.</t>
+  </si>
+  <si>
+    <t>Attempted to create a project with no name, got validation message: "Name is required" and "Project ID is required".</t>
+  </si>
+  <si>
+    <t>Entered an extremely long project title, app gota limit and displayed "Title should be less than 255 characters", blocking submission.</t>
+  </si>
+  <si>
+    <t>As Expected, Project details are displayed correctly for authorized user.</t>
+  </si>
+  <si>
+    <t>Attempted to view a project as a non-authorized member, blocked with the same "Not Authorized!"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authorized user can edit project information. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unauthorized user cannot edit project information. </t>
+  </si>
+  <si>
+    <t>Deleted a project as Admin and confirmed with "Project deleted successfully" and the project no longer appeared in the Projects list.</t>
+  </si>
+  <si>
+    <t>Made changes, navigated away, refreshed, and came back, everything saved was still there correctly.</t>
+  </si>
+  <si>
+    <t>With multiple projects open side by side, each one kept its own correct info and access.</t>
+  </si>
+  <si>
+    <t>Ran project -&gt; cycle -&gt; work item -&gt; completion flow; Cycle 1 reached 100% completion.</t>
+  </si>
+  <si>
+    <t>As Expected, Access shows updated permissions without extra privileges.</t>
+  </si>
+  <si>
+    <t>Ran a multi-step cross-account and every step captured in Activity History with correct attribution across both accounts.</t>
+  </si>
+  <si>
+    <t>As Expected Result, Work item is created successfully and is visible in the project.</t>
+  </si>
+  <si>
+    <t>Attempted to create a work item with no title, Save was blocked by required-field validation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edited a work item's title several times, each change was logged in the Activity. </t>
+  </si>
+  <si>
+    <t>As Expected Result, Attempted to open a work item as restriced user and message : "Seems like you don't have access to this Project".</t>
+  </si>
+  <si>
+    <t>Entered 250+ characters in the Title field: message is "Title should be less than 255 characters". The Description field, showed no equivalent limit/warning and accepted 500+ characters with input lag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As Expected Result, assignment is saved and displayed correctly for parent and eligible assignee. </t>
+  </si>
+  <si>
+    <t>Assignment to an unauthorized/ineligible user is blocked.</t>
+  </si>
+  <si>
+    <t>Changed work item status across In Progress -&gt; Done -&gt; In Progress, all transitions were accepted and logged.</t>
+  </si>
+  <si>
+    <t>Attempted an invalid state transition on a work item, the interface didn't allow it to go through, only valid transitions were accepted.</t>
+  </si>
+  <si>
+    <t>Set and changed priority a few times, each value saved after reload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added and removed labels, changes saved correctly and respected what the account's permissions allowed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid dates are accepted and invalid date combinations are rejected and not allowed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">work-item deletion is available only to users with the required permission. </t>
+  </si>
+  <si>
+    <t>Linked the work item to a valid cycle, the association saved and showed up correctly on the item.</t>
+  </si>
+  <si>
+    <t>All intended updates persist without unintended data loss when repoen/ refresh happen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As Expected Result, Cycle is created successfully with valid details. </t>
+  </si>
+  <si>
+    <t>Attempted to create a cycle with no title, blocked with inline validation: "Title is required."</t>
+  </si>
+  <si>
+    <t>Valid dates are accepted, Invalid date combinations are rejected or handled according to rules.</t>
+  </si>
+  <si>
+    <t>Valid dates are accepted, Invalid date combinations are not allowed.</t>
+  </si>
+  <si>
+    <t>Eligible work items is added to the selected cycle.</t>
+  </si>
+  <si>
+    <t>Attempted to access Cycles as restricted user, blocked with 'Seems like you don't have access to this Project'.</t>
+  </si>
+  <si>
+    <t>Saved cycle information remains correct after refresh/reload.</t>
+  </si>
+  <si>
+    <t>System followed the defined cycle-completion behavior without losing any work.</t>
+  </si>
+  <si>
+    <t>Negative progress percentages are displayed after changing a work item’s priority/status. For example, the Progress panel showed “Backlog: -100% of 1” or “Started: -100% of 1”, indicating incorrect state counts.</t>
   </si>
 </sst>
 </file>
@@ -1326,17 +1298,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1389,7 +1356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1397,22 +1364,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1639,466 +1603,414 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="22" style="12" customWidth="1"/>
-    <col min="2" max="2" width="90" style="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="24" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="24" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="24" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="24" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="24" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18" style="12" customWidth="1"/>
-    <col min="3" max="3" width="32" style="12" customWidth="1"/>
-    <col min="4" max="4" width="38" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32" style="12" customWidth="1"/>
-    <col min="6" max="6" width="55" style="12" customWidth="1"/>
-    <col min="7" max="7" width="39.796875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="42" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12" style="12" customWidth="1"/>
-    <col min="13" max="13" width="30" style="12" customWidth="1"/>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="32" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32" style="11" customWidth="1"/>
+    <col min="6" max="6" width="55" style="11" customWidth="1"/>
+    <col min="7" max="7" width="41.09765625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="42" style="11" customWidth="1"/>
+    <col min="9" max="9" width="41.796875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12" style="11" customWidth="1"/>
+    <col min="13" max="13" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="58.8" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="8" t="s">
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="43.2" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" ht="81" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" ht="89.4" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="43.2" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="64.2" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>57</v>
+        <v>323</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L5" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="43.2" customHeight="1">
+    <row r="6" spans="1:13" ht="60" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>65</v>
+        <v>324</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="43.2" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>71</v>
+        <v>326</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>73</v>
+        <v>328</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="43.2" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L8" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" ht="43.2" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>87</v>
+        <v>327</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>89</v>
+        <v>330</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L9" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="57.6" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>96</v>
+        <v>331</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M10" s="1"/>
     </row>
@@ -2120,447 +2032,467 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18" style="12" customWidth="1"/>
-    <col min="3" max="3" width="32" style="12" customWidth="1"/>
-    <col min="4" max="4" width="38" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32" style="12" customWidth="1"/>
-    <col min="6" max="6" width="55" style="12" customWidth="1"/>
-    <col min="7" max="7" width="28" style="12" customWidth="1"/>
-    <col min="8" max="8" width="42" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12" style="12" customWidth="1"/>
-    <col min="13" max="14" width="30" style="12" customWidth="1"/>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="32" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32" style="11" customWidth="1"/>
+    <col min="6" max="6" width="55" style="11" customWidth="1"/>
+    <col min="7" max="7" width="28" style="11" customWidth="1"/>
+    <col min="8" max="8" width="42" style="11" customWidth="1"/>
+    <col min="9" max="9" width="30" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12" style="11" customWidth="1"/>
+    <col min="13" max="14" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" ht="81" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="10"/>
-    </row>
-    <row r="2" spans="1:14" ht="57.6" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="M2" s="1"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" ht="81" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" ht="81" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="81" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="I5" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" ht="81" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="9"/>
-    </row>
-    <row r="3" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" ht="81" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" ht="28.8" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="I7" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" ht="81" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" ht="81" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" ht="28.8" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="I9" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="81" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6" spans="1:14" ht="28.8" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="I10" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="1:14" ht="81" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" ht="57.6" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="G11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="1:14" ht="57.6" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>169</v>
+        <v>341</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L11" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M11" s="1"/>
-      <c r="N11" s="9"/>
+      <c r="N11" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2578,643 +2510,671 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18" style="12" customWidth="1"/>
-    <col min="3" max="3" width="32" style="12" customWidth="1"/>
-    <col min="4" max="4" width="38" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32" style="12" customWidth="1"/>
-    <col min="6" max="6" width="55" style="12" customWidth="1"/>
-    <col min="7" max="7" width="30.09765625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="42" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12" style="12" customWidth="1"/>
-    <col min="13" max="14" width="30" style="12" customWidth="1"/>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="32" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32" style="11" customWidth="1"/>
+    <col min="6" max="6" width="55" style="11" customWidth="1"/>
+    <col min="7" max="7" width="30.09765625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="42" style="11" customWidth="1"/>
+    <col min="9" max="9" width="30" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12" style="11" customWidth="1"/>
+    <col min="13" max="14" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>170</v>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="57.6" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" ht="51" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" ht="109.2" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="47.4" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" ht="57.6" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="9"/>
-    </row>
-    <row r="3" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" ht="57.6" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="1"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6" spans="1:14" ht="43.2" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L6" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M6" s="1"/>
-      <c r="N6" s="9"/>
+      <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="57.6" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>215</v>
+        <v>176</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>219</v>
+        <v>350</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M7" s="1"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8" spans="1:14" ht="43.2" customHeight="1">
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" ht="114.6" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>222</v>
+        <v>182</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>183</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>226</v>
+        <v>351</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L8" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M8" s="1"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9" spans="1:14" ht="57.6" customHeight="1">
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14" ht="75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>229</v>
+        <v>188</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>189</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L9" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M9" s="1"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="1:14" ht="34.799999999999997" customHeight="1">
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14" ht="73.8" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>236</v>
+        <v>194</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>239</v>
+        <v>198</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>240</v>
+        <v>353</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L10" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M10" s="1"/>
-      <c r="N10" s="9"/>
+      <c r="N10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="57.6" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>243</v>
+        <v>200</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>246</v>
+        <v>354</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L11" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M11" s="1"/>
-      <c r="N11" s="9"/>
+      <c r="N11" s="8"/>
     </row>
     <row r="12" spans="1:14" ht="72" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>249</v>
+        <v>205</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M12" s="1"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14" ht="57.6" customHeight="1">
+      <c r="N12" s="8"/>
+    </row>
+    <row r="13" spans="1:14" ht="81" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>256</v>
+        <v>211</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>261</v>
+        <v>356</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M13" s="1"/>
-      <c r="N13" s="9"/>
+      <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" ht="57.6" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>264</v>
+        <v>218</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>267</v>
+        <v>222</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>268</v>
+        <v>358</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M14" s="1"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="1:14" ht="43.2" customHeight="1">
+      <c r="N14" s="8"/>
+    </row>
+    <row r="15" spans="1:14" ht="66.599999999999994" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>271</v>
+        <v>224</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L15" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M15" s="1"/>
-      <c r="N15" s="9"/>
+      <c r="N15" s="8"/>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>276</v>
+        <v>229</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>278</v>
+        <v>230</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>279</v>
+        <v>232</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>281</v>
+        <v>359</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L16" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M16" s="1"/>
-      <c r="N16" s="9"/>
+      <c r="N16" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -3233,415 +3193,429 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18" style="12" customWidth="1"/>
-    <col min="3" max="3" width="32" style="12" customWidth="1"/>
-    <col min="4" max="4" width="38" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32" style="12" customWidth="1"/>
-    <col min="6" max="6" width="55" style="12" customWidth="1"/>
-    <col min="7" max="7" width="28.69921875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="42" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12" style="12" customWidth="1"/>
-    <col min="13" max="14" width="30" style="12" customWidth="1"/>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="32" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32" style="11" customWidth="1"/>
+    <col min="6" max="6" width="55" style="11" customWidth="1"/>
+    <col min="7" max="7" width="28.69921875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="42" style="11" customWidth="1"/>
+    <col min="9" max="9" width="30" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12" style="11" customWidth="1"/>
+    <col min="13" max="14" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>170</v>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="57.6" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>285</v>
+        <v>236</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>289</v>
+        <v>241</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>290</v>
+        <v>360</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L2" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="43.2" customHeight="1">
+    <row r="3" spans="1:14" ht="55.2" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>293</v>
+        <v>243</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L3" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="43.2" customHeight="1">
+    <row r="4" spans="1:14" ht="65.400000000000006" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>300</v>
+        <v>249</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>250</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>304</v>
+        <v>363</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L4" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="57.6" customHeight="1">
+    <row r="5" spans="1:14" ht="75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>307</v>
+        <v>254</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>308</v>
+        <v>256</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L5" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="57.6" customHeight="1">
+    <row r="6" spans="1:14" ht="75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>314</v>
+        <v>260</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>261</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>316</v>
+        <v>263</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="43.2" customHeight="1">
+    <row r="7" spans="1:14" ht="78.599999999999994" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>321</v>
+        <v>267</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>268</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>322</v>
+        <v>269</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>323</v>
+        <v>270</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L7" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="57.6" customHeight="1">
+    <row r="8" spans="1:14" ht="70.2" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>326</v>
+        <v>272</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>328</v>
+        <v>273</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>274</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>329</v>
+        <v>275</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L8" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="1:14" ht="57.6" customHeight="1">
+    <row r="9" spans="1:14" ht="81.599999999999994" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="L9" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" s="13" customFormat="1" ht="84.6" customHeight="1">
+    <row r="10" spans="1:14" s="12" customFormat="1" ht="262.2" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>196</v>
+        <v>160</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>347</v>
+        <v>290</v>
       </c>
       <c r="N10" s="1"/>
     </row>
@@ -3662,218 +3636,226 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16" style="12" customWidth="1"/>
-    <col min="2" max="2" width="18" style="12" customWidth="1"/>
-    <col min="3" max="3" width="32" style="12" customWidth="1"/>
-    <col min="4" max="4" width="38" style="12" customWidth="1"/>
-    <col min="5" max="5" width="32" style="12" customWidth="1"/>
-    <col min="6" max="6" width="55" style="12" customWidth="1"/>
-    <col min="7" max="7" width="28" style="12" customWidth="1"/>
-    <col min="8" max="8" width="42" style="12" customWidth="1"/>
-    <col min="9" max="9" width="30" style="12" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12" style="12" customWidth="1"/>
-    <col min="13" max="14" width="30" style="12" customWidth="1"/>
+    <col min="1" max="1" width="16" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18" style="11" customWidth="1"/>
+    <col min="3" max="3" width="32" style="11" customWidth="1"/>
+    <col min="4" max="4" width="38" style="11" customWidth="1"/>
+    <col min="5" max="5" width="32" style="11" customWidth="1"/>
+    <col min="6" max="6" width="55" style="11" customWidth="1"/>
+    <col min="7" max="7" width="28" style="11" customWidth="1"/>
+    <col min="8" max="8" width="42" style="11" customWidth="1"/>
+    <col min="9" max="9" width="30" style="11" customWidth="1"/>
+    <col min="10" max="10" width="16" style="11" customWidth="1"/>
+    <col min="11" max="11" width="14" style="11" customWidth="1"/>
+    <col min="12" max="12" width="12" style="11" customWidth="1"/>
+    <col min="13" max="14" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="14.4" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="115.8" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="100.8" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="72" customHeight="1">
+    <row r="3" spans="1:14" ht="88.8" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>299</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>359</v>
+        <v>300</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>362</v>
+        <v>304</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L3" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="43.2" customHeight="1">
+    <row r="4" spans="1:14" ht="67.8" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>366</v>
+        <v>306</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>307</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>367</v>
+        <v>308</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>368</v>
+        <v>309</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>310</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L4" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>373</v>
+        <v>312</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>318</v>
+      </c>
       <c r="L5" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="2"/>

--- a/test-cases/Test_Cases.xlsx
+++ b/test-cases/Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro\Documents\GitHub\enterprise-saas-qa\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3B4EE0-46B0-4A9F-950A-082C111232B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C3D153-1D70-436F-9D00-A4055574E322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="595" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="595" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WSP - Workspace" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="366">
   <si>
     <t>Actual Result</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Pass</t>
-  </si>
-  <si>
-    <t>P1</t>
   </si>
   <si>
     <t>TC-WSP-002</t>
@@ -1109,9 +1106,6 @@
     <t>Made several edits to a work item's name, then logged out and refreshed. On logging back in, all edits and the full activity history were still there and unchanged, so the change persisted correctly across the session boundary.</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
     <t>Access is denied or the workspace is not available restricted data is not exposed.</t>
   </si>
   <si>
@@ -1119,9 +1113,6 @@
   </si>
   <si>
     <t>Workspace information on screen matched the saved configuration exactly.</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Invitation sent successfully invite received a 'Join QA Demo Workspace on Plane' email with a working Accept invite link.</t>
@@ -1695,322 +1686,322 @@
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="81" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="89.4" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="64.2" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="60" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="43.2" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="43.2" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" ht="43.2" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="57.6" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1"/>
     </row>
@@ -2096,400 +2087,400 @@
     </row>
     <row r="2" spans="1:14" ht="81" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:14" ht="81" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="81" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="81" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="81" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="81" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="8"/>
     </row>
     <row r="8" spans="1:14" ht="81" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="81" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="81" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="81" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="8"/>
@@ -2499,10 +2490,10 @@
     <dataValidation type="list" sqref="J2:J11" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Executed,Pass,Fail,Blocked"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K11" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="K2:K11" xr:uid="{C39AFDB5-CB3C-420F-9B26-6ED82F76FAFC}">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L11" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" sqref="L2:L11" xr:uid="{91C96630-EA08-4DC6-B9FC-E8D2C0AD89A9}">
       <formula1>"P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2571,607 +2562,607 @@
         <v>12</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="57.6" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:14" ht="51" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="109.2" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="47.4" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" ht="57.6" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="57.6" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="8"/>
     </row>
     <row r="8" spans="1:14" ht="114.6" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="75" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="8"/>
     </row>
     <row r="10" spans="1:14" ht="73.8" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="57.6" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="8"/>
     </row>
     <row r="12" spans="1:14" ht="72" customHeight="1">
       <c r="A12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="8"/>
     </row>
     <row r="13" spans="1:14" ht="81" customHeight="1">
       <c r="A13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" ht="57.6" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="I14" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="8"/>
     </row>
     <row r="15" spans="1:14" ht="66.599999999999994" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="8"/>
     </row>
     <row r="16" spans="1:14" ht="72" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="8"/>
@@ -3254,368 +3245,368 @@
         <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="57.6" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="55.2" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="65.400000000000006" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" ht="75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="J6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:14" ht="78.599999999999994" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" ht="70.2" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="81.599999999999994" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" s="12" customFormat="1" ht="262.2" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="N10" s="1"/>
     </row>
@@ -3697,165 +3688,165 @@
         <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.8" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" ht="88.8" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" ht="67.8" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="72" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="J5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="2"/>
